--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\siva\MalaiyammanTraders\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032E79A6-9754-42EB-A336-ED610CC35B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F14DC64-63ED-4E93-9FE6-3DA223EBEF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,33 +160,15 @@
     <t>1 Pkt (5pcs)</t>
   </si>
   <si>
-    <t>2" inch</t>
-  </si>
-  <si>
     <t>Lakshmi</t>
   </si>
   <si>
-    <t>3" inch</t>
-  </si>
-  <si>
-    <t>4" inch</t>
-  </si>
-  <si>
     <t>Baghubali</t>
   </si>
   <si>
-    <t>4.5" inch</t>
-  </si>
-  <si>
     <t>Jallikattu</t>
   </si>
   <si>
-    <t>5" inch</t>
-  </si>
-  <si>
-    <t>6" inch Super</t>
-  </si>
-  <si>
     <t>Red Bijilie</t>
   </si>
   <si>
@@ -202,12 +184,6 @@
     <t>Pencil</t>
   </si>
   <si>
-    <t>7" inch</t>
-  </si>
-  <si>
-    <t>15" inch Silver Rain</t>
-  </si>
-  <si>
     <t>Cartoon</t>
   </si>
   <si>
@@ -376,54 +352,6 @@
     <t>SHOTS</t>
   </si>
   <si>
-    <t>1.5” Yellow</t>
-  </si>
-  <si>
-    <t>1.5” Red &amp; Green</t>
-  </si>
-  <si>
-    <t>1.5” Red</t>
-  </si>
-  <si>
-    <t>1.5” White</t>
-  </si>
-  <si>
-    <t>1.5” Green</t>
-  </si>
-  <si>
-    <t>2.5” Crackling</t>
-  </si>
-  <si>
-    <t>2.5” Red &amp; Green</t>
-  </si>
-  <si>
-    <t>2.5” Yellow</t>
-  </si>
-  <si>
-    <t>2.5” White</t>
-  </si>
-  <si>
-    <t>2.5” Green</t>
-  </si>
-  <si>
-    <t>3.5” Red</t>
-  </si>
-  <si>
-    <t>3.5 ” White</t>
-  </si>
-  <si>
-    <t>3.5 ” Crackling</t>
-  </si>
-  <si>
-    <t>3.5” Yellow</t>
-  </si>
-  <si>
-    <t>3.5 ” Red &amp; Green</t>
-  </si>
-  <si>
-    <t>3.5 ” Green</t>
-  </si>
-  <si>
     <t>SKY DANCING SHOTS</t>
   </si>
   <si>
@@ -527,6 +455,78 @@
   </si>
   <si>
     <t>1 Pcs Pkd</t>
+  </si>
+  <si>
+    <t>1.5 inch Yellow</t>
+  </si>
+  <si>
+    <t>1.5 inch Red &amp; Green</t>
+  </si>
+  <si>
+    <t>1.5 inch Red</t>
+  </si>
+  <si>
+    <t>1.5 inch White</t>
+  </si>
+  <si>
+    <t>1.5 inch Green</t>
+  </si>
+  <si>
+    <t>2.5 inch Crackling</t>
+  </si>
+  <si>
+    <t>2.5 inch Red &amp; Green</t>
+  </si>
+  <si>
+    <t>2.5 inch Yellow</t>
+  </si>
+  <si>
+    <t>2.5 inch White</t>
+  </si>
+  <si>
+    <t>2.5 inch Green</t>
+  </si>
+  <si>
+    <t>3.5 inch Red</t>
+  </si>
+  <si>
+    <t>3.5 inch White</t>
+  </si>
+  <si>
+    <t>3.5 inch Crackling</t>
+  </si>
+  <si>
+    <t>3.5 inch Yellow</t>
+  </si>
+  <si>
+    <t>3.5 inch Red &amp; Green</t>
+  </si>
+  <si>
+    <t>3.5 inch Green</t>
+  </si>
+  <si>
+    <t>4.5 inch</t>
+  </si>
+  <si>
+    <t>5 inch</t>
+  </si>
+  <si>
+    <t>2 inch</t>
+  </si>
+  <si>
+    <t>4 inch</t>
+  </si>
+  <si>
+    <t>3 inch</t>
+  </si>
+  <si>
+    <t>6 inch Super</t>
+  </si>
+  <si>
+    <t>7 inch</t>
+  </si>
+  <si>
+    <t>15 inch Silver Rain</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1937,7 @@
         <v>16</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="H42" s="2">
         <v>307</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="43" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="6">
         <v>30</v>
@@ -1963,7 +1963,7 @@
         <v>11</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="H43" s="2">
         <v>308</v>
@@ -1971,7 +1971,7 @@
     </row>
     <row r="44" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="6">
         <v>40</v>
@@ -1989,7 +1989,7 @@
         <v>11</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="H44" s="2">
         <v>309</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="45" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B45" s="6">
         <v>70</v>
@@ -2015,7 +2015,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="H45" s="2">
         <v>310</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="46" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B46" s="6">
         <v>80</v>
@@ -2041,7 +2041,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="H46" s="2">
         <v>311</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="47" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B47" s="6">
         <v>100</v>
@@ -2067,7 +2067,7 @@
         <v>11</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="H47" s="2">
         <v>312</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="48" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B48" s="6">
         <v>60</v>
@@ -2084,10 +2084,10 @@
         <v>30</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>16</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="49" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B49" s="6">
         <v>80</v>
@@ -2110,16 +2110,16 @@
         <v>40</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H49" s="2">
         <v>402</v>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="50" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B50" s="6">
         <v>80</v>
@@ -2136,7 +2136,7 @@
         <v>40</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>10</v>
@@ -2145,7 +2145,7 @@
         <v>16</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="H50" s="2">
         <v>403</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="51" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B51" s="6">
         <v>150</v>
@@ -2162,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>10</v>
@@ -2171,7 +2171,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="H51" s="2">
         <v>404</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="52" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B52" s="6">
         <v>40</v>
@@ -2188,7 +2188,7 @@
         <v>20</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>10</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="53" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B53" s="7">
         <v>100</v>
@@ -2210,10 +2210,10 @@
         <v>50</v>
       </c>
       <c r="D53" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="54" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B54" s="6">
         <v>30</v>
@@ -2232,7 +2232,7 @@
         <v>15</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>10</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="55" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B55" s="6">
         <v>60</v>
@@ -2254,7 +2254,7 @@
         <v>30</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>10</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="56" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B56" s="6">
         <v>60</v>
@@ -2276,7 +2276,7 @@
         <v>30</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>23</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="57" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B57" s="6">
         <v>60</v>
@@ -2298,7 +2298,7 @@
         <v>30</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>10</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="58" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B58" s="6">
         <v>300</v>
@@ -2320,10 +2320,10 @@
         <v>150</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="59" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B59" s="6">
         <v>80</v>
@@ -2342,7 +2342,7 @@
         <v>40</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>10</v>
@@ -2351,7 +2351,7 @@
         <v>11</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H59" s="2">
         <v>501</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="60" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B60" s="6">
         <v>150</v>
@@ -2368,7 +2368,7 @@
         <v>75</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>10</v>
@@ -2377,7 +2377,7 @@
         <v>16</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H60" s="2">
         <v>502</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="61" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B61" s="6">
         <v>150</v>
@@ -2394,7 +2394,7 @@
         <v>75</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>10</v>
@@ -2403,7 +2403,7 @@
         <v>11</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H61" s="2">
         <v>503</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="62" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B62" s="6">
         <v>200</v>
@@ -2420,7 +2420,7 @@
         <v>100</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         <v>11</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H62" s="2">
         <v>504</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="63" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B63" s="6">
         <v>300</v>
@@ -2446,7 +2446,7 @@
         <v>150</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>16</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H63" s="2">
         <v>505</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="64" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B64" s="6">
         <v>250</v>
@@ -2472,16 +2472,16 @@
         <v>125</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H64" s="2">
         <v>601</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="65" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B65" s="6">
         <v>350</v>
@@ -2498,10 +2498,10 @@
         <v>175</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>11</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="66" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B66" s="6">
         <v>200</v>
@@ -2524,16 +2524,16 @@
         <v>100</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H66" s="2">
         <v>603</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="67" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B67" s="6">
         <v>200</v>
@@ -2550,7 +2550,7 @@
         <v>100</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>23</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="68" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B68" s="6">
         <v>350</v>
@@ -2572,10 +2572,10 @@
         <v>175</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="69" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B69" s="6">
         <v>200</v>
@@ -2594,10 +2594,10 @@
         <v>100</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="70" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B70" s="6">
         <v>200</v>
@@ -2616,7 +2616,7 @@
         <v>100</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>23</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="71" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B71" s="6">
         <v>200</v>
@@ -2638,7 +2638,7 @@
         <v>100</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>10</v>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="72" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B72" s="6">
         <v>200</v>
@@ -2660,7 +2660,7 @@
         <v>100</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>23</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="73" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B73" s="6">
         <v>200</v>
@@ -2682,7 +2682,7 @@
         <v>100</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>10</v>
@@ -2695,7 +2695,7 @@
     </row>
     <row r="74" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B74" s="6">
         <v>150</v>
@@ -2704,7 +2704,7 @@
         <v>75</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>23</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="75" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B75" s="6">
         <v>350</v>
@@ -2726,7 +2726,7 @@
         <v>175</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>23</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="76" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B76" s="6">
         <v>350</v>
@@ -2748,10 +2748,10 @@
         <v>175</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="77" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B77" s="6">
         <v>200</v>
@@ -2770,7 +2770,7 @@
         <v>100</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>23</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="78" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B78" s="6">
         <v>200</v>
@@ -2792,7 +2792,7 @@
         <v>100</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>23</v>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="79" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B79" s="6">
         <v>300</v>
@@ -2814,10 +2814,10 @@
         <v>150</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="80" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B80" s="6">
         <v>200</v>
@@ -2836,7 +2836,7 @@
         <v>100</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>23</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="81" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B81" s="7">
         <v>200</v>
@@ -2858,10 +2858,10 @@
         <v>100</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="82" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B82" s="6">
         <v>300</v>
@@ -2880,10 +2880,10 @@
         <v>150</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="83" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B83" s="7">
         <v>300</v>
@@ -2902,10 +2902,10 @@
         <v>150</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="84" spans="1:8" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B84" s="7">
         <v>400</v>
@@ -2924,10 +2924,10 @@
         <v>200</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="85" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B85" s="6">
         <v>40</v>
@@ -2946,10 +2946,10 @@
         <v>20</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="86" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B86" s="6">
         <v>60</v>
@@ -2968,10 +2968,10 @@
         <v>30</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="87" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B87" s="6">
         <v>100</v>
@@ -2990,10 +2990,10 @@
         <v>50</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="88" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B88" s="6">
         <v>100</v>
@@ -3012,10 +3012,10 @@
         <v>50</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="89" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B89" s="6">
         <v>80</v>
@@ -3034,10 +3034,10 @@
         <v>40</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>11</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="90" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B90" s="6">
         <v>400</v>
@@ -3060,10 +3060,10 @@
         <v>200</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>11</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="91" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B91" s="6">
         <v>800</v>
@@ -3086,10 +3086,10 @@
         <v>400</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>11</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="92" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B92" s="6">
         <v>2000</v>
@@ -3112,10 +3112,10 @@
         <v>1000</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>16</v>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="93" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B93" s="6">
         <v>100</v>
@@ -3138,16 +3138,16 @@
         <v>50</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H93" s="2">
         <v>801</v>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="94" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B94" s="6">
         <v>200</v>
@@ -3164,16 +3164,16 @@
         <v>100</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H94" s="2">
         <v>802</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="95" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B95" s="6">
         <v>400</v>
@@ -3190,16 +3190,16 @@
         <v>200</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H95" s="2">
         <v>803</v>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="96" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B96" s="6">
         <v>400</v>
@@ -3216,7 +3216,7 @@
         <v>200</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>10</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="97" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B97" s="6">
         <v>600</v>
@@ -3238,7 +3238,7 @@
         <v>300</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>10</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="98" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B98" s="6">
         <v>100</v>
@@ -3260,16 +3260,16 @@
         <v>50</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="H98" s="2">
         <v>901</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="99" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B99" s="6">
         <v>100</v>
@@ -3286,16 +3286,16 @@
         <v>50</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="H99" s="2">
         <v>902</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="100" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B100" s="6">
         <v>100</v>
@@ -3312,16 +3312,16 @@
         <v>50</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="H100" s="2">
         <v>903</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="101" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B101" s="6">
         <v>100</v>
@@ -3338,16 +3338,16 @@
         <v>50</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="H101" s="2">
         <v>904</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="102" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B102" s="6">
         <v>100</v>
@@ -3364,16 +3364,16 @@
         <v>50</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="H102" s="2">
         <v>905</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="103" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B103" s="6">
         <v>200</v>
@@ -3390,16 +3390,16 @@
         <v>100</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="H103" s="2">
         <v>906</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="104" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B104" s="6">
         <v>200</v>
@@ -3416,16 +3416,16 @@
         <v>100</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="H104" s="2">
         <v>907</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="105" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B105" s="6">
         <v>200</v>
@@ -3442,16 +3442,16 @@
         <v>100</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H105" s="2">
         <v>908</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="106" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B106" s="6">
         <v>200</v>
@@ -3468,16 +3468,16 @@
         <v>100</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="H106" s="2">
         <v>909</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="107" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B107" s="6">
         <v>200</v>
@@ -3494,16 +3494,16 @@
         <v>100</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="H107" s="2">
         <v>910</v>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="108" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B108" s="6">
         <v>600</v>
@@ -3520,16 +3520,16 @@
         <v>300</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="H108" s="2">
         <v>911</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="109" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B109" s="6">
         <v>600</v>
@@ -3546,16 +3546,16 @@
         <v>300</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="H109" s="2">
         <v>912</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="110" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B110" s="6">
         <v>600</v>
@@ -3572,16 +3572,16 @@
         <v>300</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="H110" s="2">
         <v>913</v>
@@ -3589,7 +3589,7 @@
     </row>
     <row r="111" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B111" s="6">
         <v>600</v>
@@ -3598,16 +3598,16 @@
         <v>300</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H111" s="2">
         <v>914</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="112" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B112" s="6">
         <v>600</v>
@@ -3624,16 +3624,16 @@
         <v>300</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H112" s="2">
         <v>915</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="113" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B113" s="6">
         <v>600</v>
@@ -3650,16 +3650,16 @@
         <v>300</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="H113" s="2">
         <v>916</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="114" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B114" s="6">
         <v>300</v>
@@ -3676,16 +3676,16 @@
         <v>150</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="H114" s="2">
         <v>917</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="115" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B115" s="6">
         <v>1000</v>
@@ -3702,16 +3702,16 @@
         <v>500</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="H115" s="2">
         <v>918</v>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="116" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B116" s="6">
         <v>2000</v>
@@ -3728,16 +3728,16 @@
         <v>1000</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="H116" s="2">
         <v>919</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="117" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B117" s="6">
         <v>4000</v>
@@ -3754,16 +3754,16 @@
         <v>2000</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="H117" s="2">
         <v>920</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="118" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B118" s="6">
         <v>7000</v>
@@ -3780,16 +3780,16 @@
         <v>3500</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="H118" s="2">
         <v>921</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="119" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B119" s="6">
         <v>40</v>
@@ -3806,10 +3806,10 @@
         <v>20</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="120" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B120" s="6">
         <v>60</v>
@@ -3828,10 +3828,10 @@
         <v>30</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="121" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B121" s="6">
         <v>120</v>
@@ -3850,10 +3850,10 @@
         <v>60</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="122" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B122" s="6">
         <v>300</v>
@@ -3872,10 +3872,10 @@
         <v>150</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="123" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B123" s="6">
         <v>400</v>
@@ -3894,10 +3894,10 @@
         <v>200</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="124" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B124" s="6">
         <v>200</v>
@@ -3916,10 +3916,10 @@
         <v>100</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="125" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B125" s="6">
         <v>20</v>
@@ -3938,10 +3938,10 @@
         <v>10</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="126" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B126" s="6">
         <v>180</v>
@@ -3960,10 +3960,10 @@
         <v>90</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="127" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B127" s="6">
         <v>40</v>
@@ -3982,10 +3982,10 @@
         <v>20</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="128" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="B128" s="6">
         <v>40</v>
@@ -4004,10 +4004,10 @@
         <v>20</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="129" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="B129" s="6">
         <v>80</v>
@@ -4026,10 +4026,10 @@
         <v>40</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="130" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B130" s="6">
         <v>120</v>
@@ -4048,10 +4048,10 @@
         <v>60</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="131" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B131" s="9">
         <v>200</v>
@@ -4070,10 +4070,10 @@
         <v>100</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="132" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="B132" s="11">
         <v>400</v>
@@ -4092,10 +4092,10 @@
         <v>200</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="133" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B133" s="11">
         <v>500</v>
@@ -4114,10 +4114,10 @@
         <v>250</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="F133" s="10"/>
       <c r="G133" s="10"/>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="134" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="B134" s="11">
         <v>700</v>
@@ -4136,10 +4136,10 @@
         <v>350</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="F134" s="10"/>
       <c r="G134" s="10"/>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="135" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B135" s="11">
         <v>800</v>
@@ -4158,10 +4158,10 @@
         <v>450</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="F135" s="10"/>
       <c r="G135" s="10"/>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="136" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B136" s="11">
         <v>1100</v>
@@ -4180,10 +4180,10 @@
         <v>550</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F136" s="10"/>
       <c r="G136" s="10"/>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="137" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B137" s="11">
         <v>2000</v>
@@ -4202,10 +4202,10 @@
         <v>1000</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
